--- a/Database/data/EMU3000/EMU 3000 維修物料清單/5年維護/01 清潔塊單元--C20、C21--OK/清潔塊單元C20、C21大修料件清單--60個月.xlsx
+++ b/Database/data/EMU3000/EMU 3000 維修物料清單/5年維護/01 清潔塊單元--C20、C21--OK/清潔塊單元C20、C21大修料件清單--60個月.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\暑期工讀\EMU 3000 維修物料清單\EMU 3000 維修物料清單\5y\清潔塊單元--C20、C21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\SBIR\Database\data\EMU3000\EMU 3000 維修物料清單\5年維護\01 清潔塊單元--C20、C21--OK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6D9CA1A-92DD-4DD5-AA66-1F19A3B2424B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA276AA6-B6FB-497F-88B8-B5924D0969FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="定更件" sheetId="1" r:id="rId1"/>
@@ -474,7 +474,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7840087" y="0"/>
+          <a:off x="8506983" y="0"/>
           <a:ext cx="3580951" cy="3053082"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="5083173" cy="4071421"/>
@@ -924,7 +924,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7924800" y="5369858"/>
+          <a:off x="8675984" y="5496143"/>
           <a:ext cx="3361765" cy="2807598"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="5083175" cy="4071620"/>
@@ -1379,7 +1379,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6957061" y="0"/>
+          <a:off x="7578091" y="0"/>
           <a:ext cx="2392679" cy="2092962"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="5083173" cy="4071421"/>
@@ -1829,7 +1829,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7048501" y="4244340"/>
+          <a:off x="7669531" y="4453890"/>
           <a:ext cx="2354580" cy="1925022"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="5083175" cy="4071620"/>
@@ -2262,9 +2262,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2302,9 +2302,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2337,26 +2337,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2389,26 +2372,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2583,18 +2549,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K261"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>68</v>
       </c>
@@ -2620,7 +2586,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="2" t="s">
         <v>27</v>
@@ -2639,7 +2605,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>1</v>
       </c>
@@ -2660,7 +2626,7 @@
       </c>
       <c r="J3" s="13"/>
     </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>2</v>
       </c>
@@ -2680,7 +2646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>5</v>
       </c>
@@ -2700,7 +2666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>6</v>
       </c>
@@ -2720,7 +2686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>7</v>
       </c>
@@ -2741,7 +2707,7 @@
       </c>
       <c r="J7" s="13"/>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>8</v>
       </c>
@@ -2761,7 +2727,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>9</v>
       </c>
@@ -2781,7 +2747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>12</v>
       </c>
@@ -2801,7 +2767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>19</v>
       </c>
@@ -2821,7 +2787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>21</v>
       </c>
@@ -2841,7 +2807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>22</v>
       </c>
@@ -2861,7 +2827,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>23</v>
       </c>
@@ -2881,7 +2847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>24</v>
       </c>
@@ -2901,7 +2867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>31</v>
       </c>
@@ -2921,7 +2887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>35</v>
       </c>
@@ -2941,7 +2907,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>37</v>
       </c>
@@ -2961,7 +2927,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>38</v>
       </c>
@@ -2984,7 +2950,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>39</v>
       </c>
@@ -3005,7 +2971,7 @@
       </c>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>63</v>
       </c>
@@ -3020,7 +2986,7 @@
       </c>
       <c r="J21" s="13"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>2</v>
       </c>
@@ -3040,7 +3006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>3</v>
       </c>
@@ -3060,7 +3026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>4</v>
       </c>
@@ -3080,7 +3046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="15">
         <v>5</v>
       </c>
@@ -3100,7 +3066,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="15"/>
       <c r="B26" s="2" t="s">
         <v>66</v>
@@ -3115,7 +3081,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14">
         <v>1</v>
       </c>
@@ -3135,7 +3101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14">
         <v>2</v>
       </c>
@@ -3155,7 +3121,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14">
         <v>5</v>
       </c>
@@ -3175,7 +3141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A30" s="14">
         <v>6</v>
       </c>
@@ -3196,7 +3162,7 @@
       </c>
       <c r="J30" s="13"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="14">
         <v>7</v>
       </c>
@@ -3216,7 +3182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A32" s="14">
         <v>8</v>
       </c>
@@ -3239,7 +3205,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A33" s="14">
         <v>9</v>
       </c>
@@ -3260,7 +3226,7 @@
       </c>
       <c r="J33" s="13"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="14">
         <v>12</v>
       </c>
@@ -3280,7 +3246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="14">
         <v>19</v>
       </c>
@@ -3300,7 +3266,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="14">
         <v>21</v>
       </c>
@@ -3320,7 +3286,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="14">
         <v>22</v>
       </c>
@@ -3340,7 +3306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="14">
         <v>23</v>
       </c>
@@ -3360,7 +3326,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="14">
         <v>24</v>
       </c>
@@ -3380,7 +3346,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="14">
         <v>31</v>
       </c>
@@ -3400,7 +3366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="14">
         <v>35</v>
       </c>
@@ -3420,7 +3386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="14">
         <v>37</v>
       </c>
@@ -3440,7 +3406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="14">
         <v>38</v>
       </c>
@@ -3460,7 +3426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="14">
         <v>39</v>
       </c>
@@ -3480,7 +3446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="B45" s="2" t="s">
         <v>63</v>
       </c>
@@ -3497,7 +3463,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="14">
         <v>2</v>
       </c>
@@ -3517,7 +3483,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="14">
         <v>3</v>
       </c>
@@ -3537,7 +3503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A48" s="14">
         <v>4</v>
       </c>
@@ -3558,7 +3524,7 @@
       </c>
       <c r="I48" s="13"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
         <v>5</v>
       </c>
@@ -3578,10 +3544,10 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="15"/>
     </row>
-    <row r="164" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
@@ -3589,7 +3555,7 @@
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
     </row>
-    <row r="168" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
@@ -3597,7 +3563,7 @@
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
     </row>
-    <row r="172" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
@@ -3605,7 +3571,7 @@
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
     </row>
-    <row r="191" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
@@ -3613,7 +3579,7 @@
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
     </row>
-    <row r="198" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
@@ -3621,7 +3587,7 @@
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
     </row>
-    <row r="201" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
@@ -3629,7 +3595,7 @@
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
     </row>
-    <row r="206" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
@@ -3637,7 +3603,7 @@
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
     </row>
-    <row r="209" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
@@ -3645,7 +3611,7 @@
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
     </row>
-    <row r="214" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
       <c r="D214" s="2"/>
@@ -3653,7 +3619,7 @@
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
     </row>
-    <row r="218" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
@@ -3661,7 +3627,7 @@
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
     </row>
-    <row r="222" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -3669,7 +3635,7 @@
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
     </row>
-    <row r="226" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
@@ -3677,7 +3643,7 @@
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
     </row>
-    <row r="235" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
@@ -3685,7 +3651,7 @@
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
     </row>
-    <row r="238" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
@@ -3693,7 +3659,7 @@
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
     </row>
-    <row r="240" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
       <c r="D240" s="5"/>
@@ -3702,7 +3668,7 @@
       <c r="G240" s="5"/>
       <c r="H240" s="5"/>
     </row>
-    <row r="242" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
       <c r="D242" s="5"/>
@@ -3711,7 +3677,7 @@
       <c r="G242" s="5"/>
       <c r="H242" s="5"/>
     </row>
-    <row r="243" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
       <c r="D243" s="5"/>
@@ -3720,7 +3686,7 @@
       <c r="G243" s="5"/>
       <c r="H243" s="5"/>
     </row>
-    <row r="244" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
       <c r="D244" s="5"/>
@@ -3729,7 +3695,7 @@
       <c r="G244" s="5"/>
       <c r="H244" s="5"/>
     </row>
-    <row r="245" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
@@ -3737,10 +3703,10 @@
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
     </row>
-    <row r="246" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="2:8" x14ac:dyDescent="0.25">
       <c r="H246" s="5"/>
     </row>
-    <row r="247" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
       <c r="D247" s="2"/>
@@ -3748,7 +3714,7 @@
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
     </row>
-    <row r="249" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
       <c r="D249" s="5"/>
@@ -3757,7 +3723,7 @@
       <c r="G249" s="5"/>
       <c r="H249" s="5"/>
     </row>
-    <row r="251" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
       <c r="D251" s="5"/>
@@ -3765,7 +3731,7 @@
       <c r="F251" s="5"/>
       <c r="H251" s="5"/>
     </row>
-    <row r="252" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
       <c r="D252" s="5"/>
@@ -3773,7 +3739,7 @@
       <c r="F252" s="5"/>
       <c r="H252" s="5"/>
     </row>
-    <row r="253" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
       <c r="D253" s="5"/>
@@ -3781,7 +3747,7 @@
       <c r="F253" s="5"/>
       <c r="H253" s="5"/>
     </row>
-    <row r="254" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
@@ -3789,7 +3755,7 @@
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
     </row>
-    <row r="255" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
@@ -3798,7 +3764,7 @@
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
     </row>
-    <row r="256" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
       <c r="D256" s="2"/>
@@ -3806,21 +3772,21 @@
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
     </row>
-    <row r="257" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C257" s="5"/>
       <c r="D257" s="5"/>
       <c r="E257" s="5"/>
       <c r="F257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C258" s="5"/>
       <c r="D258" s="5"/>
       <c r="E258" s="5"/>
       <c r="F258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
       <c r="D259" s="2"/>
@@ -3828,13 +3794,13 @@
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
     </row>
-    <row r="260" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C260" s="5"/>
       <c r="D260" s="5"/>
       <c r="E260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C261" s="5"/>
       <c r="D261" s="5"/>
       <c r="E261" s="5"/>
@@ -3855,17 +3821,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L146"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="43.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>68</v>
       </c>
@@ -3888,7 +3854,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
@@ -3905,7 +3871,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>3</v>
       </c>
@@ -3922,7 +3888,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>15</v>
       </c>
@@ -3939,7 +3905,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>18</v>
       </c>
@@ -3956,7 +3922,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>27</v>
       </c>
@@ -3973,7 +3939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>30</v>
       </c>
@@ -3990,7 +3956,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>33</v>
       </c>
@@ -4007,7 +3973,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>36</v>
       </c>
@@ -4024,7 +3990,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
@@ -4039,7 +4005,7 @@
       </c>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>1</v>
       </c>
@@ -4057,7 +4023,7 @@
       </c>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>66</v>
       </c>
@@ -4072,7 +4038,7 @@
       </c>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>3</v>
       </c>
@@ -4092,7 +4058,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>15</v>
       </c>
@@ -4109,7 +4075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>18</v>
       </c>
@@ -4126,7 +4092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>27</v>
       </c>
@@ -4143,7 +4109,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>30</v>
       </c>
@@ -4160,7 +4126,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>33</v>
       </c>
@@ -4177,7 +4143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>36</v>
       </c>
@@ -4194,7 +4160,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>63</v>
       </c>
@@ -4208,7 +4174,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>1</v>
       </c>
@@ -4225,17 +4191,17 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J25" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="36" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J36" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -4243,7 +4209,7 @@
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
     </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -4251,7 +4217,7 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
     </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -4259,7 +4225,7 @@
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
     </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
@@ -4267,7 +4233,7 @@
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
     </row>
-    <row r="113" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -4275,7 +4241,7 @@
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
@@ -4283,7 +4249,7 @@
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
     </row>
-    <row r="119" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
@@ -4291,7 +4257,7 @@
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
     </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -4299,7 +4265,7 @@
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
     </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
@@ -4307,7 +4273,7 @@
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
     </row>
-    <row r="127" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
@@ -4315,7 +4281,7 @@
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
     </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
@@ -4323,7 +4289,7 @@
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
@@ -4331,7 +4297,7 @@
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
     </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
@@ -4339,7 +4305,7 @@
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
     </row>
-    <row r="146" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
